--- a/results/Feature_Importance_Ranking.xlsx
+++ b/results/Feature_Importance_Ranking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuba\studia\Praca_magisterska\Fault-detection-in-mechanical-devices\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jakub\Kuba_lokalne\studia\Praca_magisterska\Projekt\Fault-detection-in-mechanical-devices\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04486A98-67D9-4C41-A690-276D121F539B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BD89C5D-3975-4391-A94A-5B1F9B499199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{64FAE43A-E4FB-4BC4-B7EA-8BEB846B6904}"/>
+    <workbookView xWindow="15045" yWindow="3855" windowWidth="20670" windowHeight="12135" xr2:uid="{B72ED5BF-42EC-4CC4-834D-34622D396A03}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature_Importance_Ranking" sheetId="1" r:id="rId1"/>
@@ -85,19 +85,19 @@
     <t>CURRENT (A) kurtosis</t>
   </si>
   <si>
+    <t>ROTO (RPM) skew</t>
+  </si>
+  <si>
     <t>CURRENT (A) peak_to_peak</t>
   </si>
   <si>
-    <t>ROTO (RPM) skew</t>
-  </si>
-  <si>
     <t>CURRENT (A) Amp @ 2x RPM</t>
   </si>
   <si>
+    <t>CURRENT (A) Amp @ 1x RPM</t>
+  </si>
+  <si>
     <t>CURRENT (A) Amp @ 3x RPM</t>
-  </si>
-  <si>
-    <t>CURRENT (A) Amp @ 1x RPM</t>
   </si>
   <si>
     <t>ROTO (RPM) Amp @ 2x RPM</t>
@@ -991,15 +991,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1665D6EA-562D-468C-894F-CAD2790F3A1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E4C921-5A08-45AC-8D05-07D1FEF0C0DC}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1037,12 +1036,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="2">
-        <v>0.13875743956842601</v>
+        <v>0.134510157556853</v>
       </c>
       <c r="C2" s="2">
         <v>0.176527702462483</v>
@@ -1051,10 +1050,10 @@
         <v>0.103374414</v>
       </c>
       <c r="E2" s="2">
-        <v>0.29216152019002301</v>
+        <v>0.27092511013215798</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>-4.2390333667505997E-17</v>
       </c>
       <c r="G2" s="2">
         <v>0.121723561043681</v>
@@ -1075,12 +1074,12 @@
         <v>2.1202206188183998</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>0.12918022568867099</v>
+        <v>0.12648682733986899</v>
       </c>
       <c r="C3" s="2">
         <v>0.114812264754297</v>
@@ -1089,7 +1088,7 @@
         <v>9.4823829999999998E-2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.18527315914489201</v>
+        <v>0.171806167400881</v>
       </c>
       <c r="F3" s="2">
         <v>0.152272727272727</v>
@@ -1113,12 +1112,12 @@
         <v>1.71952225258228</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>9.4079260505809004E-2</v>
+        <v>9.3043338063961895E-2</v>
       </c>
       <c r="C4" s="2">
         <v>7.3586365328809106E-2</v>
@@ -1127,7 +1126,7 @@
         <v>0.11366758</v>
       </c>
       <c r="E4" s="2">
-        <v>7.1258907363420401E-2</v>
+        <v>6.6079295154184994E-2</v>
       </c>
       <c r="F4" s="2">
         <v>0.156818181818181</v>
@@ -1151,12 +1150,12 @@
         <v>0.95914481077074198</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>8.5911036161087903E-2</v>
+        <v>8.3977314269640002E-2</v>
       </c>
       <c r="C5" s="2">
         <v>9.8264972429861597E-2</v>
@@ -1165,7 +1164,7 @@
         <v>5.2189190000000003E-2</v>
       </c>
       <c r="E5" s="2">
-        <v>0.13301662707838399</v>
+        <v>0.123348017621145</v>
       </c>
       <c r="F5" s="2">
         <v>3.8636363636363601E-2</v>
@@ -1189,12 +1188,12 @@
         <v>1.8715647313493899</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>8.3430810550054801E-2</v>
+        <v>8.23603573601462E-2</v>
       </c>
       <c r="C6" s="2">
         <v>6.7519322796160602E-2</v>
@@ -1203,7 +1202,7 @@
         <v>6.8447105999999994E-2</v>
       </c>
       <c r="E6" s="2">
-        <v>7.3634204275534396E-2</v>
+        <v>6.8281938325991207E-2</v>
       </c>
       <c r="F6" s="2">
         <v>0.13636363636363599</v>
@@ -1227,12 +1226,12 @@
         <v>1.24000683200552</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>7.3716822923836606E-2</v>
+        <v>7.3647761427713496E-2</v>
       </c>
       <c r="C7" s="2">
         <v>3.5629721534882898E-2</v>
@@ -1241,7 +1240,7 @@
         <v>0.24514097000000001</v>
       </c>
       <c r="E7" s="2">
-        <v>4.7505938242280599E-3</v>
+        <v>4.4052863436123699E-3</v>
       </c>
       <c r="F7" s="2">
         <v>3.6363636363636299E-2</v>
@@ -1265,12 +1264,12 @@
         <v>0.81342175118260196</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>7.1775673094818804E-2</v>
+        <v>7.0325381676232895E-2</v>
       </c>
       <c r="C8" s="2">
         <v>8.4577570208797803E-2</v>
@@ -1279,7 +1278,7 @@
         <v>6.1450247E-2</v>
       </c>
       <c r="E8" s="2">
-        <v>9.9762470308788501E-2</v>
+        <v>9.2511013215859E-2</v>
       </c>
       <c r="F8" s="2">
         <v>2.0454545454545399E-2</v>
@@ -1303,12 +1302,12 @@
         <v>1.6135210349673601</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="2">
-        <v>6.6383874433665793E-2</v>
+        <v>6.5693259472434498E-2</v>
       </c>
       <c r="C9" s="2">
         <v>6.72630395467229E-2</v>
@@ -1317,7 +1316,7 @@
         <v>4.6733535999999999E-2</v>
       </c>
       <c r="E9" s="2">
-        <v>4.7505938242280298E-2</v>
+        <v>4.4052863436123399E-2</v>
       </c>
       <c r="F9" s="2">
         <v>0.109090909090909</v>
@@ -1341,12 +1340,12 @@
         <v>1.0681953551435599</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
       <c r="B10" s="2">
-        <v>5.4092021063028503E-2</v>
+        <v>5.23299065255836E-2</v>
       </c>
       <c r="C10" s="2">
         <v>8.5422987284389101E-2</v>
@@ -1355,7 +1354,7 @@
         <v>7.9990649999999996E-2</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>-8.8105726872246305E-3</v>
       </c>
       <c r="F10" s="2">
         <v>5.9090909090909E-2</v>
@@ -1379,88 +1378,88 @@
         <v>0.80046892798928904</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>4.4858154328484397E-2</v>
+        <v>4.4113812529358497E-2</v>
       </c>
       <c r="C11" s="2">
-        <v>3.4396040203053903E-2</v>
+        <v>5.1196622005834497E-2</v>
       </c>
       <c r="D11" s="2">
-        <v>1.9979312999999999E-2</v>
+        <v>2.5768633999999999E-2</v>
       </c>
       <c r="E11" s="2">
-        <v>6.1757719714964299E-2</v>
+        <v>2.6431718061673999E-2</v>
       </c>
       <c r="F11" s="2">
-        <v>6.8181818181818094E-2</v>
+        <v>6.3636363636363602E-2</v>
       </c>
       <c r="G11" s="2">
-        <v>3.99758805266478E-2</v>
+        <v>5.3535725011045199E-2</v>
       </c>
       <c r="H11">
-        <v>3.4396040203053903E-2</v>
+        <v>5.1196622005834497E-2</v>
       </c>
       <c r="I11">
-        <v>1.9979315000000001E-2</v>
+        <v>2.5768638E-2</v>
       </c>
       <c r="J11">
-        <v>4.6428571428571402E-2</v>
+        <v>2.1428571428571401E-2</v>
       </c>
       <c r="K11">
-        <v>5.3571428571428499E-2</v>
+        <v>4.9999999999999899E-2</v>
       </c>
       <c r="L11">
-        <v>0.69631290295232096</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.93250268919652501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>4.4528181506097303E-2</v>
+        <v>4.3960354878883598E-2</v>
       </c>
       <c r="C12" s="2">
-        <v>5.1196622005834497E-2</v>
+        <v>3.4396040203053903E-2</v>
       </c>
       <c r="D12" s="2">
-        <v>2.5768633999999999E-2</v>
+        <v>1.9979312999999999E-2</v>
       </c>
       <c r="E12" s="2">
-        <v>2.85035629453682E-2</v>
+        <v>5.7268722466960402E-2</v>
       </c>
       <c r="F12" s="2">
-        <v>6.3636363636363602E-2</v>
+        <v>6.8181818181818094E-2</v>
       </c>
       <c r="G12" s="2">
-        <v>5.3535725011045199E-2</v>
+        <v>3.99758805266478E-2</v>
       </c>
       <c r="H12">
-        <v>5.1196622005834497E-2</v>
+        <v>3.4396040203053903E-2</v>
       </c>
       <c r="I12">
-        <v>2.5768638E-2</v>
+        <v>1.9979315000000001E-2</v>
       </c>
       <c r="J12">
-        <v>2.1428571428571401E-2</v>
+        <v>4.6428571428571402E-2</v>
       </c>
       <c r="K12">
-        <v>4.9999999999999899E-2</v>
+        <v>5.3571428571428499E-2</v>
       </c>
       <c r="L12">
-        <v>0.93250268919652501</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.69631290295232096</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="2">
-        <v>2.7717484745527401E-2</v>
+        <v>2.7682953997465901E-2</v>
       </c>
       <c r="C13" s="2">
         <v>2.0785727266203698E-2</v>
@@ -1469,7 +1468,7 @@
         <v>3.7109267000000001E-2</v>
       </c>
       <c r="E13" s="2">
-        <v>2.3752969121140399E-3</v>
+        <v>2.2026431718062001E-3</v>
       </c>
       <c r="F13" s="2">
         <v>4.0909090909090798E-2</v>
@@ -1493,88 +1492,88 @@
         <v>0.65158544973576105</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="2">
-        <v>1.9937842279205899E-2</v>
+        <v>1.62296691747701E-2</v>
       </c>
       <c r="C14" s="2">
-        <v>1.43129078726895E-2</v>
+        <v>1.76885037902045E-2</v>
       </c>
       <c r="D14" s="2">
-        <v>2.5507338000000001E-2</v>
+        <v>2.5817886000000002E-2</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
+        <v>-1.7621145374449199E-2</v>
       </c>
       <c r="F14" s="2">
-        <v>2.4999999999999901E-2</v>
+        <v>1.8181818181818101E-2</v>
       </c>
       <c r="G14" s="2">
-        <v>3.4868965178289399E-2</v>
+        <v>3.7081283281366201E-2</v>
       </c>
       <c r="H14">
-        <v>1.43129078726895E-2</v>
+        <v>1.76885037902045E-2</v>
       </c>
       <c r="I14">
-        <v>2.5507341999999999E-2</v>
+        <v>2.581789E-2</v>
       </c>
       <c r="J14">
-        <v>-1.9642857142857E-2</v>
+        <v>-1.42857142857142E-2</v>
       </c>
       <c r="K14">
-        <v>1.9642857142857E-2</v>
+        <v>1.42857142857142E-2</v>
       </c>
       <c r="L14">
-        <v>0.60735898862948901</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.64589386566816998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="2">
-        <v>1.975389824966E-2</v>
+        <v>1.5092027301232399E-2</v>
       </c>
       <c r="C15" s="2">
-        <v>1.76885037902045E-2</v>
+        <v>1.43129078726895E-2</v>
       </c>
       <c r="D15" s="2">
-        <v>2.5817886000000002E-2</v>
+        <v>2.5507338000000001E-2</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>-2.42290748898677E-2</v>
       </c>
       <c r="F15" s="2">
-        <v>1.8181818181818101E-2</v>
+        <v>2.4999999999999901E-2</v>
       </c>
       <c r="G15" s="2">
-        <v>3.7081283281366201E-2</v>
+        <v>3.4868965178289399E-2</v>
       </c>
       <c r="H15">
-        <v>1.76885037902045E-2</v>
+        <v>1.43129078726895E-2</v>
       </c>
       <c r="I15">
-        <v>2.581789E-2</v>
+        <v>2.5507341999999999E-2</v>
       </c>
       <c r="J15">
-        <v>-1.42857142857142E-2</v>
+        <v>-1.9642857142857E-2</v>
       </c>
       <c r="K15">
-        <v>1.42857142857142E-2</v>
+        <v>1.9642857142857E-2</v>
       </c>
       <c r="L15">
-        <v>0.64589386566816998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.60735898862948901</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>1.71831306959641E-2</v>
+        <v>1.3658901621074301E-2</v>
       </c>
       <c r="C16" s="2">
         <v>1.9762275644443598E-2</v>
@@ -1583,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>0</v>
+        <v>-1.7621145374449199E-2</v>
       </c>
       <c r="F16" s="2">
         <v>2.4999999999999901E-2</v>
@@ -1607,7 +1606,7 @@
         <v>0.716822934462779</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1645,12 +1644,12 @@
         <v>0.505045950818659</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="2">
-        <v>1.0007542460355E-2</v>
+        <v>9.1264851916326301E-3</v>
       </c>
       <c r="C18" s="2">
         <v>8.3365636081613598E-3</v>
@@ -1659,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>-4.4052863436123101E-3</v>
       </c>
       <c r="F18" s="2">
         <v>3.8636363636363601E-2</v>
@@ -1683,7 +1682,7 @@
         <v>5.3383424005293903E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
